--- a/bakup/customers/danial.xlsx
+++ b/bakup/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="101">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -292,6 +292,36 @@
   </si>
   <si>
     <t>1405/06/02</t>
+  </si>
+  <si>
+    <t>1405/06/09</t>
+  </si>
+  <si>
+    <t>مزه پل دوآب</t>
+  </si>
+  <si>
+    <t>1405/06/13</t>
+  </si>
+  <si>
+    <t>1405/06/18</t>
+  </si>
+  <si>
+    <t>1405/06/21</t>
+  </si>
+  <si>
+    <t>دنگ سس</t>
+  </si>
+  <si>
+    <t>1405/07/02</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>1405/07/12</t>
+  </si>
+  <si>
+    <t>1405/07/17</t>
   </si>
 </sst>
 </file>
@@ -769,7 +799,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2575000</v>
+        <v>2833000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1976,87 +2006,135 @@
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
-      </c>
-      <c r="B83" s="6"/>
+        <v>2745000</v>
+      </c>
+      <c r="B83" s="6">
+        <v>170000</v>
+      </c>
       <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="3"/>
+      <c r="D83" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
-      </c>
-      <c r="B84" s="6"/>
+        <v>2900000</v>
+      </c>
+      <c r="B84" s="6">
+        <v>155000</v>
+      </c>
       <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="3"/>
+      <c r="D84" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
-      </c>
-      <c r="B85" s="6"/>
+        <v>3087000</v>
+      </c>
+      <c r="B85" s="6">
+        <v>187000</v>
+      </c>
       <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="3"/>
+      <c r="D85" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
-      </c>
-      <c r="B86" s="6"/>
+        <v>3183000</v>
+      </c>
+      <c r="B86" s="6">
+        <v>96000</v>
+      </c>
       <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="3"/>
+      <c r="D86" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
-      </c>
-      <c r="B87" s="6"/>
+        <v>3408000</v>
+      </c>
+      <c r="B87" s="6">
+        <v>225000</v>
+      </c>
       <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="3"/>
+      <c r="D87" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
-      </c>
-      <c r="B88" s="6"/>
+        <v>3608000</v>
+      </c>
+      <c r="B88" s="6">
+        <v>200000</v>
+      </c>
       <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="3"/>
+      <c r="D88" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2608000</v>
       </c>
       <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="3"/>
+      <c r="C89" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
-      </c>
-      <c r="B90" s="6"/>
+        <v>2833000</v>
+      </c>
+      <c r="B90" s="6">
+        <v>225000</v>
+      </c>
       <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="3"/>
+      <c r="D90" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2833000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2066,7 +2144,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2833000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2076,7 +2154,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2833000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2086,7 +2164,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2833000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2096,7 +2174,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2833000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2107,11 +2185,11 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>6493000</v>
+        <v>7751000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
-        <v>3918000</v>
+        <v>4918000</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
@@ -2119,7 +2197,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2575000</v>
+        <v>2833000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">
